--- a/portal/templates/09 Forecast.xlsx
+++ b/portal/templates/09 Forecast.xlsx
@@ -9,8 +9,9 @@
   <sheets>
     <sheet name="Read me" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Assumptions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Methods" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Overrides" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Pipeline" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Methods" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Overrides" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B20"/>
+  <dimension ref="B2:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -577,54 +578,68 @@
     <row r="12">
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>The Overrides tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="45" customHeight="1">
+          <t>The Pipeline tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="75" customHeight="1">
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>One row per figure you want typed. Department blank means the company. Amount as the P&amp;L shows it: income positive, a cost positive. The override replaces the method's figure for that account and month and is flagged as typed on the Forecast page.</t>
+          <t>How the systems' view of income replaces the baseline. Confirmed work is OnRent orders by event month and accepted Qwilr quotes by acceptance month plus the lead time; open Zoho deals count at their probability by close month. The near months are what is booked plus the never in the pipeline share of last year; further out the forecast never falls below the baseline. A won deal in Zoho counts only once an order or quote carries it, so nothing is counted twice.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="3" t="inlineStr">
         <is>
+          <t>The Overrides tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>One row per figure you want typed. Department blank means the company. Amount as the P&amp;L shows it: income positive, a cost positive. The override replaces the method's figure for that account and month and is flagged as typed on the Forecast page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
           <t>Fractions, not percentages</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="B15" s="4" t="inlineStr">
+    <row r="17" ht="30" customHeight="1">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Growth and revenue rates are typed as fractions, the same as the Config template: 0.03 is three per cent, 0.35 is thirty five per cent.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="3" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Cream cells with blue text: paste or type here.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="6" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>Yellow cells: a setting you choose.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="7" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Grey cells: calculated or fixed. Do not type here.</t>
         </is>
@@ -809,6 +824,275 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Use the pipeline for income</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>No leaves income on the Seasonal method alone</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Near months</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Months after the reporting month forecast as booked plus the never in the pipeline share, with no floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Cancellation rate</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Fraction taken off booked and weighted work; 0.05 is five per cent</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Count won deals without an order or quote</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Yes counts a Closed Won deal as confirmed even when no OnRent order or Qwilr quote carries it</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Never in the pipeline: default</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Share of the same month last year that never goes through a system. Assumed until measured</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Never in the pipeline: ONSITE</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Repeat onsite work is mostly not quoted</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Never in the pipeline: PRODUCTION</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Never in the pipeline: VIDEO</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C9" s="9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Never in the pipeline: INTEGRATION</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C10" s="9" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Never in the pipeline: CONSULTING</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C11" s="9" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Months from close to revenue: default</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Whole months between a deal closing or a quote being accepted and the revenue landing</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Months from close to revenue: INTEGRATION</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Delivery follows acceptance</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Confirmed order statuses</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Confirmed, Booked, In progress, Completed</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>OnRent statuses counted as confirmed, comma separated</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>Accepted quote statuses</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Qwilr statuses counted as confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Probability: Qualification</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Optional. A fraction typed here overrides Zoho's probability for that stage</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Probability: Proposal/Price Quote</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="9" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Probability: Negotiation/Review</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="9" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2763,7 +3047,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2825,12 +3109,10 @@
       <c r="C2" s="11" t="n">
         <v>46327</v>
       </c>
-      <c r="D2" s="10" t="n">
-        <v>0</v>
-      </c>
+      <c r="D2" s="10" t="n"/>
       <c r="E2" s="10" t="inlineStr">
         <is>
-          <t>Example: blank the amount or delete the row. Department blank means the company.</t>
+          <t>Example row, ignored while the amount is blank. Department blank means the company.</t>
         </is>
       </c>
     </row>

--- a/portal/templates/09 Forecast.xlsx
+++ b/portal/templates/09 Forecast.xlsx
@@ -824,7 +824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -904,12 +904,12 @@
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>Yes counts a Closed Won deal as confirmed even when no OnRent order or Qwilr quote carries it</t>
+          <t>Yes counts a Closed Won deal as confirmed in its closing month; a deal whose job number an order or quote already carries is never counted twice</t>
         </is>
       </c>
     </row>
@@ -1054,23 +1054,27 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>Probability: Qualification</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="n"/>
+          <t>Probability: Building Value Proposition</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n">
+        <v>0.1</v>
+      </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Optional. A fraction typed here overrides Zoho's probability for that stage</t>
+          <t>Zoho's real stage names. The report carries no probability, so these are the weights for open deals</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>Probability: Proposal/Price Quote</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="n"/>
+          <t>Probability: Proposal Sent</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n">
+        <v>0.4</v>
+      </c>
       <c r="C17" s="9" t="inlineStr"/>
     </row>
     <row r="18">
@@ -1079,8 +1083,21 @@
           <t>Probability: Negotiation/Review</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n"/>
+      <c r="B18" s="10" t="n">
+        <v>0.6</v>
+      </c>
       <c r="C18" s="9" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Probability: Verbal Approval</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C19" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/portal/templates/09 Forecast.xlsx
+++ b/portal/templates/09 Forecast.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Read me" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Assumptions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Pipeline" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Methods" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Overrides" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pipeline" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methods" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overrides" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
